--- a/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
+++ b/Mau_Bang_Khao_Sat_Hoc_Vien_VietMac.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dữ Liệu Khảo Sát" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Tổng Quan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Kết Nối &amp; Tặng Quà" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dữ Liệu Khảo Sát &amp; Ảnh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Danh Bạ &amp; Kênh" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,7 +30,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -40,47 +39,28 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00059669"/>
-      <sz val="11"/>
+      <color rgb="001E3A8A"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00F8FAFC"/>
-      <sz val="14"/>
+      <color rgb="00059669"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0064748B"/>
+      <color rgb="002563EB"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000284C7"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00059669"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00D97706"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -95,14 +75,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00334155"/>
-        <bgColor rgb="00334155"/>
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,9 +106,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,29 +118,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -533,24 +497,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -576,286 +536,161 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Số Điện Thoại / Zalo</t>
+          <t>Số Zalo Hay Dùng</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Nghề Nghiệp / Dự Án</t>
+          <t>Mảng Kinh Doanh &amp; Định Hướng AI</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Link Kênh / Profile</t>
+          <t>Danh Sách Link Kênh / Video / FB</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Nguồn Biết Đến</t>
+          <t>Hành Trình Biết Đến &amp; Xem Video</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Video Ấn Tượng Nhất</t>
+          <t>Góp Ý Thẳng Thắn &amp; Lời Nhắn</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Điều Tâm Đắc Nhất</t>
+          <t>Số Lượng Ảnh</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Góp Ý Vận Hành &amp; Lớp Học</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Điểm Đánh Giá (1-10)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Nhu Cầu Khóa Nâng Cao</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Kênh Liên Hệ Ưu Tiên</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Lời Nhắn Nhủ Riêng</t>
+          <t>Link Drive &amp; Tên File Ảnh Kỷ Niệm</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KS-2026-001</t>
+          <t>KS-2026-0001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 23:16:30</t>
+          <t>24/08/2026 08:15:20</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>30 Ngày Học Làm Nội Dung Viral / Offline Thực Chiến</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Học viên ngành Phân Bón Nông Nghiệp</t>
+          <t>Lớp Offline Thực Chiến - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Trang</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0988***888</t>
+          <t>0912345678</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Kinh doanh &amp; Sản xuất Phân bón Nông nghiệp (Có nhiều cảnh đẹp &amp; tư liệu thực tế nhưng chỉ biết giơ máy lên quay, chưa biết dựng)</t>
+          <t>Luật sư pháp chế (Chuẩn bị mở văn phòng luật riêng). Muốn làm dạng video case 45s như kênh tiktok.com/@luatsucuocsong. Cần AI bóc tách kịch bản và setup 2 góc máy.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://facebook.com/30ngayviral.fedu.vn</t>
+          <t>https://facebook.com/thutrang.law
+https://tiktok.com/@thutrang_legal</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Lướt Facebook Reels va vào video của anh Việt</t>
+          <t>Lướt thấy video anh Việt chia sẻ về băm phân cảnh 3 tầng và góc nhìn AI thực chiến. Xem đúng 20 giây là thấy cách nói quá mộc mạc, không đao to búa lớn nên nhắn tin đăng ký và chuyển khoản luôn.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Xem liền 5 video chia sẻ cách bóc kịch bản mộc mạc và định hướng làm nội dung</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Nội dung mộc mạc, thực chiến đánh trúng vấn đề. Không cần 7 tiếng hay 11 điểm chạm để chốt đơn, xem đúng 5 clip là điền form chốt đi học ngay!</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Tư vấn và gọi điện cực kỳ nhanh gọn, đăng ký xong là chốt đơn đi học luôn không cần tư vấn lòng vòng.</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>AI Băm kịch bản, Xây dựng kênh thực chiến ngành nông nghiệp &amp; phân bón</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Zalo</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Em thề là trước đây em không hề biết anh là ai luôn ấy :))) cũng không mất 7 tiếng để chốt đơn đâu, xem đúng 5 clip là chốt, lúc chốt còn chưa kịp theo dõi page thầy haha!</t>
+          <t>• Khâu tư vấn: Các bạn nên tư vấn rõ ưu đãi giảm 10% khi đăng ký nhóm từ đầu để học viên rủ thêm bạn.
+• Lớp học: Nhịp dạy rất thực chiến, tâm đắc nhất là tự tin cầm máy và tư duy băm nhỏ phân cảnh.
+• Lời nhắn: Cảm ơn anh nhiều, hôm nào rảnh em mời anh ly cafe nhé!</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>2 ảnh</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>📁 Link Drive: https://drive.google.com/drive/folders/1aBcDeFgHiJkLmNoPqRsTuVwXyZ_NguyenThuTrang
+1. lop_hoc_thuc_hanh_quay_2_may.jpg (185 KB)
+2. anh_chup_chung_anh_viet.jpg (210 KB)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
+    <row r="3" ht="95" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KS-2026-002</t>
+          <t>KS-2026-0002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 09:30:15</t>
+          <t>24/08/2026 08:20:45</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Offline Thực Chiến K12 - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Thu Trang</t>
+          <t>Lớp Offline Thực Chiến - Hà Nội</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Trần Quốc Huy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>0912345678</t>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Quản lý pháp chế MEDLATEC (Chuẩn bị mở cty luật)</t>
+          <t>Chủ thương hiệu thời trang nam tại Hải Phòng. Muốn làm kênh chia sẻ cách phối đồ và video ads chuyển đổi cao.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://facebook.com/thutrang.law</t>
+          <t>https://tiktok.com/@huytran.menswear
+https://youtube.com/@huytranstyle</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Video TikTok / Reel (Quyết định sau 20s xem video)</t>
+          <t>Thấy video Facebook Reels anh Việt bóc tách kịch bản 3 tầng bán quần áo. Thấy chuẩn bài quá nên tìm kênh xem thêm 3 video nữa rồi bấm đăng ký luôn.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Video anh Việt nói về băm nhỏ phân cảnh và tư duy làm video AI đa ngành</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Tư duy rất mới về ứng dụng AI, kỹ năng quay dựng và cách làm marketing đa ngành, định hướng rõ ràng</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>- Cần kiểm soát danh sách check-in chặt chẽ hơn
-- Gửi link khảo sát ngắn trước buổi học
-- Thăm hỏi học viên vắng/về sớm
-- Giới thiệu gói nâng cao 10p cuối kèm ưu đãi tại lớp
-- Tư vấn rõ ưu đãi giảm 10% khi đăng ký nhóm 2 người</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>AI Chuyên Sâu, Xây dựng thương hiệu cá nhân Luật Sư</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Zalo</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Giá trị Thầy mang lại là điều vô giá đối với Em ạ! Chúc Thầy luôn giữ ngọn lửa nhiệt huyết.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>KS-2026-003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 10:15:40</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Offline Thực Chiến K12 - Hà Nội</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Trần Quốc Huy</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Chủ thương hiệu thời trang nam tại Hải Phòng</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>https://tiktok.com/@huytran.menswear</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>YouTube Shorts / Facebook Reels</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Video phân tích kịch bản video bán hàng thời trang 3 tầng</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Biết cách setup 2 máy quay và ánh sáng chuyên nghiệp, không còn sợ đứng trước ống kính</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Khóa học rất thực chiến, mong có thêm buổi thực hành ngoài trời</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Video Ads Chuyển Đổi Cao, Automation Video</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Zalo</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Cảm ơn anh Việt rất nhiều, nhờ anh mà em tự tin bấm máy quay ngay ngày hôm sau!</t>
+          <t>• 2 ngày học rất đã, vỡ ra cách setup ánh sáng và cách bóc tách video đối thủ.
+• Góp ý: Khâu check-in buổi sáng nên gửi link khảo sát trước để anh nắm nhu cầu từng người sớm hơn.
+• Nhắn nhủ: Về Hải Phòng em bấm máy quay ngay loạt video đầu tiên gửi anh xem nhé!</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>2 ảnh</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>📁 Link Drive: https://drive.google.com/drive/folders/1xYzAbCdEfGhIjKlMnOpQrStUvWx_TranQuocHuy
+1. khong_khi_thuc_hanh_setup_den.jpg (192 KB)
+2. chup_ky_niem_ca_lop_ha_noi.jpg (245 KB)</t>
         </is>
       </c>
     </row>
@@ -870,233 +705,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>📊 BÁO CÁO TỔNG HỢP KHẢO SÁT &amp; INSIGHT HỌC VIÊN - VIETMAC</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Họ Và Tên</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Số Zalo</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Mảng Kinh Doanh</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Link Kênh / Video Đã Gửi</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Số Lượng Ảnh</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Trạng Thái Theo Dõi</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Tổng Số Phản Hồi</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Điểm Hài Lòng Trung Bình (NPS)</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Tỷ Lệ Quan Tâm Nâng Cao</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="n"/>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Trang</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Luật sư pháp chế (Mở văn phòng)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>https://facebook.com/thutrang.law
+https://tiktok.com/@thutrang_legal</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2 ảnh</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Đã lưu Zalo, đã bấm follow kênh</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8">
-        <f>COUNTA('Dữ Liệu Khảo Sát'!A2:A1000)</f>
-        <v/>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="9">
-        <f>AVERAGE('Dữ Liệu Khảo Sát'!L2:L1000)</f>
-        <v/>
-      </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="10">
-        <f>COUNTIF('Dữ Liệu Khảo Sát'!M2:M1000, "*AI*")/COUNTA('Dữ Liệu Khảo Sát'!A2:A1000)</f>
-        <v/>
-      </c>
-      <c r="F4" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C4:D4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Họ Tên Học Viên</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>Nghề Nghiệp / Dự Án</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>Link Kênh / Profile</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>Zalo / SĐT</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t>Nhu Cầu Độc Quyền</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
-        <is>
-          <t>Đã Kết Nối / Tặng Quà</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Học viên ngành Phân Bón Nông Nghiệp</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Kinh doanh &amp; Sản xuất Phân bón Nông nghiệp</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>https://facebook.com/30ngayviral.fedu.vn</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>0988***888</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Gói prompt AI băm cảnh nông nghiệp + tư duy hook 3s</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>Đã kết nối Zalo &amp; tư vấn</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="12" t="n">
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thu Trang</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Quản lý pháp chế MEDLATEC (Mở cty luật)</t>
+          <t>Trần Quốc Huy</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0987654321</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://facebook.com/thutrang.law</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>0912345678</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Gói prompt AI kịch bản luật sư + template branding</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Đã add Zalo &amp; gửi quà</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Trần Quốc Huy</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Chủ thương hiệu thời trang nam tại Hải Phòng</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>https://tiktok.com/@huytran.menswear</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>0987654321</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Checklist setup 2 máy quay + sound effect bán hàng</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>Đã follow kênh TikTok</t>
+          <t>Thời trang nam Hải Phòng</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://tiktok.com/@huytran.menswear
+https://youtube.com/@huytranstyle</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2 ảnh</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Đã lưu Zalo, đang chờ video đầu tay</t>
         </is>
       </c>
     </row>
